--- a/Data/Ecoli_phenotypes/fluxomics_datasets_gerosa.xlsx
+++ b/Data/Ecoli_phenotypes/fluxomics_datasets_gerosa.xlsx
@@ -290,9 +290,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -309,7 +309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
@@ -317,7 +317,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>13.584</v>
+        <v>-13.584</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>0.29</v>
@@ -326,7 +326,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>7</v>
       </c>
@@ -343,7 +343,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>8</v>
       </c>
@@ -360,7 +360,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>9</v>
       </c>
@@ -377,7 +377,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
@@ -394,7 +394,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
@@ -411,7 +411,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>12</v>
       </c>
@@ -428,7 +428,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>13</v>
       </c>
@@ -445,7 +445,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>14</v>
       </c>
@@ -462,7 +462,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>15</v>
       </c>
@@ -479,7 +479,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>16</v>
       </c>
@@ -496,7 +496,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>17</v>
       </c>
@@ -513,7 +513,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>18</v>
       </c>
@@ -530,7 +530,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>19</v>
       </c>
@@ -547,7 +547,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>20</v>
       </c>
@@ -564,7 +564,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>21</v>
       </c>
@@ -581,7 +581,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>22</v>
       </c>
@@ -598,7 +598,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>23</v>
       </c>
@@ -615,7 +615,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>24</v>
       </c>
@@ -632,7 +632,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>25</v>
       </c>
@@ -649,7 +649,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>26</v>
       </c>
@@ -666,7 +666,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>27</v>
       </c>
@@ -683,7 +683,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>28</v>
       </c>
@@ -700,7 +700,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>29</v>
       </c>
@@ -717,7 +717,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>30</v>
       </c>
@@ -734,7 +734,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>31</v>
       </c>
@@ -751,7 +751,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>32</v>
       </c>
@@ -768,7 +768,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>33</v>
       </c>
@@ -785,7 +785,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
         <v>34</v>
       </c>
@@ -802,7 +802,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>35</v>
       </c>
@@ -819,7 +819,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
         <v>36</v>
       </c>
@@ -836,7 +836,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>37</v>
       </c>
@@ -853,7 +853,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>38</v>
       </c>
@@ -870,7 +870,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
         <v>39</v>
       </c>
@@ -887,7 +887,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
         <v>40</v>
       </c>
@@ -904,7 +904,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
         <v>41</v>
       </c>
@@ -921,7 +921,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
         <v>42</v>
       </c>
@@ -938,7 +938,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
         <v>43</v>
       </c>
@@ -955,7 +955,7 @@
         <v>13.584</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
         <v>5</v>
       </c>
@@ -963,7 +963,7 @@
         <v>44</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>-3.32865961111111</v>
+        <v>3.32865961111111</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>0.4924</v>
@@ -972,7 +972,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
         <v>7</v>
       </c>
@@ -980,7 +980,7 @@
         <v>44</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>8.328</v>
+        <v>-8.328</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>0.4924</v>
@@ -989,7 +989,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
         <v>8</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
         <v>9</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
         <v>10</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
         <v>11</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
         <v>12</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
         <v>13</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>14</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>15</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>16</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
         <v>17</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>18</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>19</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
         <v>20</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
         <v>21</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
         <v>22</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
         <v>23</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
         <v>24</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
         <v>25</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
         <v>26</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
         <v>27</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
         <v>28</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
         <v>29</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
         <v>30</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
         <v>31</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
         <v>32</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
         <v>33</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
         <v>34</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
         <v>35</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
         <v>36</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>37</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>38</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>39</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>40</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
         <v>41</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
         <v>42</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
         <v>43</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>8.328</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
         <v>5</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
         <v>7</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>8</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>45</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>1.969</v>
+        <v>-1.969</v>
       </c>
       <c r="D80" s="0" t="n">
         <v>0.18</v>
@@ -1652,7 +1652,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
         <v>9</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
         <v>10</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
         <v>11</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
         <v>12</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
         <v>13</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
         <v>14</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
         <v>15</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
         <v>16</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
         <v>17</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
         <v>18</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
         <v>19</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
         <v>20</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
         <v>21</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
         <v>22</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
         <v>23</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
         <v>24</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
         <v>25</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
         <v>26</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
         <v>28</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
         <v>29</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
         <v>30</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
         <v>31</v>
       </c>
@@ -2043,7 +2043,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
         <v>32</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
         <v>33</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
         <v>34</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
         <v>35</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
         <v>36</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
         <v>37</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
         <v>38</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
         <v>39</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
         <v>40</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
         <v>41</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
         <v>42</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
         <v>43</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>1.969</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
         <v>5</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>46</v>
       </c>
       <c r="C116" s="0" t="n">
-        <v>-6.82701917999702</v>
+        <v>6.82701917999702</v>
       </c>
       <c r="D116" s="0" t="n">
         <v>0.65</v>
@@ -2264,7 +2264,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
         <v>7</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
         <v>8</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
         <v>9</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>46</v>
       </c>
       <c r="C119" s="0" t="n">
-        <v>9.654</v>
+        <v>-9.654</v>
       </c>
       <c r="D119" s="0" t="n">
         <v>0.65</v>
@@ -2315,7 +2315,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
         <v>10</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
         <v>11</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
         <v>12</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
         <v>13</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
         <v>14</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
         <v>15</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
         <v>16</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
         <v>17</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
         <v>18</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
         <v>19</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>20</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
         <v>21</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
         <v>22</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
         <v>23</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
         <v>24</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
         <v>25</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
         <v>26</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
         <v>27</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
         <v>28</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
         <v>29</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
         <v>30</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
         <v>31</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
         <v>32</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
         <v>33</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
         <v>34</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
         <v>35</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
         <v>36</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
         <v>37</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
         <v>38</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
         <v>39</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
         <v>40</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
         <v>41</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
         <v>42</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
         <v>43</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>9.654</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
         <v>5</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>47</v>
       </c>
       <c r="C154" s="0" t="n">
-        <v>-0.5970002640036</v>
+        <v>0.5970002640036</v>
       </c>
       <c r="D154" s="0" t="n">
         <v>0.49</v>
@@ -2910,7 +2910,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
         <v>7</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
         <v>8</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="0" t="s">
         <v>9</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
         <v>10</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>47</v>
       </c>
       <c r="C158" s="0" t="n">
-        <v>4.94483364720653</v>
+        <v>-4.94483364720653</v>
       </c>
       <c r="D158" s="0" t="n">
         <v>0.49</v>
@@ -2978,7 +2978,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
         <v>11</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
         <v>12</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
         <v>13</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
         <v>14</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
         <v>15</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
         <v>16</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
         <v>17</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="0" t="s">
         <v>18</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
         <v>19</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
         <v>20</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
         <v>21</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
         <v>22</v>
       </c>
@@ -3182,7 +3182,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
         <v>23</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
         <v>24</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
         <v>25</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
         <v>26</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="0" t="s">
         <v>27</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="0" t="s">
         <v>28</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="0" t="s">
         <v>29</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
         <v>30</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="0" t="s">
         <v>31</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
         <v>32</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="0" t="s">
         <v>33</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="0" t="s">
         <v>34</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="0" t="s">
         <v>35</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="0" t="s">
         <v>36</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="0" t="s">
         <v>37</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
         <v>38</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
         <v>39</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
         <v>40</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
         <v>41</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
         <v>42</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
         <v>43</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>4.9448</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
         <v>5</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>48</v>
       </c>
       <c r="C192" s="0" t="n">
-        <v>-5.00398239363803</v>
+        <v>5.00398239363803</v>
       </c>
       <c r="D192" s="0" t="n">
         <v>0.59</v>
@@ -3556,7 +3556,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
         <v>7</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
         <v>8</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="0" t="s">
         <v>9</v>
       </c>
@@ -3607,7 +3607,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="0" t="s">
         <v>10</v>
       </c>
@@ -3624,7 +3624,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="0" t="s">
         <v>11</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>48</v>
       </c>
       <c r="C197" s="0" t="n">
-        <v>7.28392319195215</v>
+        <v>-7.28392319195215</v>
       </c>
       <c r="D197" s="0" t="n">
         <v>0.59</v>
@@ -3641,7 +3641,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="0" t="s">
         <v>12</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="0" t="s">
         <v>13</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="0" t="s">
         <v>14</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="0" t="s">
         <v>15</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="0" t="s">
         <v>16</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="0" t="s">
         <v>17</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="0" t="s">
         <v>18</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="0" t="s">
         <v>19</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
         <v>20</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
         <v>21</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
         <v>22</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
         <v>23</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="0" t="s">
         <v>24</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="0" t="s">
         <v>25</v>
       </c>
@@ -3879,7 +3879,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="0" t="s">
         <v>26</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="0" t="s">
         <v>27</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="0" t="s">
         <v>28</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="0" t="s">
         <v>29</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="0" t="s">
         <v>30</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="0" t="s">
         <v>31</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
         <v>32</v>
       </c>
@@ -3998,7 +3998,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
         <v>33</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
         <v>34</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
         <v>35</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
         <v>36</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
         <v>37</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
         <v>38</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
         <v>39</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
         <v>40</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
         <v>41</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
         <v>42</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
         <v>43</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>7.2839</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
         <v>5</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>49</v>
       </c>
       <c r="C230" s="0" t="n">
-        <v>-11.9139097200115</v>
+        <v>11.9139097200115</v>
       </c>
       <c r="D230" s="0" t="n">
         <v>0.39</v>
@@ -4202,7 +4202,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
         <v>7</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
         <v>8</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
         <v>9</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
         <v>10</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
         <v>11</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
         <v>12</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>49</v>
       </c>
       <c r="C236" s="0" t="n">
-        <v>26.714</v>
+        <v>-26.714</v>
       </c>
       <c r="D236" s="0" t="n">
         <v>0.39</v>
@@ -4304,7 +4304,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
         <v>13</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
         <v>14</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="0" t="s">
         <v>15</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>49</v>
       </c>
       <c r="C239" s="0" t="n">
-        <v>1.15701005397392</v>
+        <v>-1.15701005397392</v>
       </c>
       <c r="D239" s="0" t="n">
         <v>0.39</v>
@@ -4355,7 +4355,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="0" t="s">
         <v>16</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="0" t="s">
         <v>17</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="0" t="s">
         <v>18</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="0" t="s">
         <v>19</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="0" t="s">
         <v>20</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="0" t="s">
         <v>21</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="0" t="s">
         <v>22</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="0" t="s">
         <v>23</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="0" t="s">
         <v>24</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="0" t="s">
         <v>25</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="0" t="s">
         <v>26</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="0" t="s">
         <v>27</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="0" t="s">
         <v>28</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="0" t="s">
         <v>29</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="0" t="s">
         <v>30</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="0" t="s">
         <v>31</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="0" t="s">
         <v>32</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="0" t="s">
         <v>33</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="0" t="s">
         <v>34</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="0" t="s">
         <v>35</v>
       </c>
@@ -4695,7 +4695,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="0" t="s">
         <v>36</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="0" t="s">
         <v>37</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="0" t="s">
         <v>38</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="0" t="s">
         <v>39</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="0" t="s">
         <v>40</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="0" t="s">
         <v>41</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="0" t="s">
         <v>42</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="0" t="s">
         <v>43</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>26.714</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="0" t="s">
         <v>5</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>50</v>
       </c>
       <c r="C268" s="0" t="n">
-        <v>-3.32097367999354</v>
+        <v>3.32097367999354</v>
       </c>
       <c r="D268" s="0" t="n">
         <v>0.51</v>
@@ -4848,7 +4848,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="0" t="s">
         <v>7</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="0" t="s">
         <v>8</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="0" t="s">
         <v>9</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="0" t="s">
         <v>10</v>
       </c>
@@ -4916,7 +4916,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="0" t="s">
         <v>11</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="0" t="s">
         <v>12</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="0" t="s">
         <v>13</v>
       </c>
@@ -4958,7 +4958,7 @@
         <v>50</v>
       </c>
       <c r="C275" s="0" t="n">
-        <v>15.902</v>
+        <v>-15.902</v>
       </c>
       <c r="D275" s="0" t="n">
         <v>0.51</v>
@@ -4967,7 +4967,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="0" t="s">
         <v>14</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>50</v>
       </c>
       <c r="C276" s="0" t="n">
-        <v>1.13999847799564</v>
+        <v>-1.13999847799564</v>
       </c>
       <c r="D276" s="0" t="n">
         <v>0.51</v>
@@ -4984,7 +4984,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="0" t="s">
         <v>15</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="0" t="s">
         <v>16</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="0" t="s">
         <v>17</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="0" t="s">
         <v>18</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="s">
         <v>19</v>
       </c>
@@ -5069,7 +5069,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
         <v>20</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="s">
         <v>21</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="s">
         <v>22</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="0" t="s">
         <v>23</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="s">
         <v>24</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="s">
         <v>25</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="s">
         <v>26</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="s">
         <v>27</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="s">
         <v>28</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="s">
         <v>29</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="s">
         <v>30</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="s">
         <v>31</v>
       </c>
@@ -5273,7 +5273,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="s">
         <v>32</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="s">
         <v>33</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="s">
         <v>34</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="s">
         <v>35</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="s">
         <v>36</v>
       </c>
@@ -5358,7 +5358,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="0" t="s">
         <v>37</v>
       </c>
@@ -5375,7 +5375,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="0" t="s">
         <v>38</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="0" t="s">
         <v>39</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="0" t="s">
         <v>40</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="0" t="s">
         <v>41</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="0" t="s">
         <v>42</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>15.902</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="0" t="s">
         <v>43</v>
       </c>

--- a/Data/Ecoli_phenotypes/fluxomics_datasets_gerosa.xlsx
+++ b/Data/Ecoli_phenotypes/fluxomics_datasets_gerosa.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="53">
   <si>
     <t xml:space="preserve">reaction</t>
   </si>
@@ -163,6 +163,12 @@
     <t xml:space="preserve">Glucose</t>
   </si>
   <si>
+    <t xml:space="preserve">ICDHyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDH</t>
+  </si>
+  <si>
     <t xml:space="preserve">Glycerol</t>
   </si>
   <si>
@@ -263,13 +269,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -289,8 +299,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E307"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -310,5170 +320,5204 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>-13.584</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="2" t="n">
         <v>1.35842519514767E-007</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E11" s="0" t="n">
+      <c r="E11" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="2" t="n">
         <v>-3.42325540770599</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="2" t="n">
         <v>1.88623516768455</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="2" t="n">
         <v>-1.88623516768297</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="2" t="n">
         <v>-1.88623516766754</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="2" t="n">
         <v>-2.26387036766646</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="2" t="n">
         <v>-2.73659356767242</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E19" s="0" t="n">
+      <c r="E19" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="2" t="n">
         <v>1.65319540547002</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E20" s="0" t="n">
+      <c r="E20" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="2" t="n">
         <v>0.0654626571538204</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E21" s="0" t="n">
+      <c r="E21" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="2" t="n">
         <v>0.82159384767752</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E22" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="2" t="n">
         <v>3.40831300771948</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E23" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="2" t="n">
         <v>2.58671916004196</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E24" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="2" t="n">
         <v>1.02932292002225</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E25" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="2" t="n">
         <v>1.55739624001971</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E26" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="2" t="n">
         <v>0.839146920012723</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="2" t="n">
         <v>0.718249320006988</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E28" s="0" t="n">
+      <c r="E28" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="2" t="n">
         <v>1.77414548696941</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E29" s="0" t="n">
+      <c r="E29" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="2" t="n">
         <v>3.11428124916625</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E30" s="0" t="n">
+      <c r="E30" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="2" t="n">
         <v>8.83401907247554</v>
       </c>
-      <c r="D31" s="0" t="n">
+      <c r="D31" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E31" s="0" t="n">
+      <c r="E31" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="2" t="n">
         <v>4.69641722365165</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E32" s="0" t="n">
+      <c r="E32" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="2" t="n">
         <v>4.26716282364871</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E33" s="0" t="n">
+      <c r="E33" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="2" t="n">
         <v>8.40476467247503</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E34" s="0" t="n">
+      <c r="E34" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="2" t="n">
         <v>8.40476467247503</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E35" s="0" t="n">
+      <c r="E35" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="2" t="n">
         <v>10.6713</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="2" t="n">
         <v>1.87103728663592</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="2" t="n">
         <v>4.13760184882973</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="2" t="n">
         <v>0.29</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="2" t="n">
         <v>13.584</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="2" t="n">
         <v>3.32865961111111</v>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="2" t="n">
         <v>-8.328</v>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="0" t="n">
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="0" t="n">
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="0" t="n">
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E44" s="0" t="n">
+      <c r="E44" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="0" t="n">
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E45" s="0" t="n">
+      <c r="E45" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="0" t="n">
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E46" s="0" t="n">
+      <c r="E46" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="0" t="n">
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E47" s="0" t="n">
+      <c r="E47" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="2" t="n">
         <v>8.32745210350901E-008</v>
       </c>
-      <c r="D48" s="0" t="n">
+      <c r="D48" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E48" s="0" t="n">
+      <c r="E48" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="0" t="n">
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E49" s="0" t="n">
+      <c r="E49" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="2" t="n">
         <v>-6.19793233476514</v>
       </c>
-      <c r="D50" s="0" t="n">
+      <c r="D50" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E50" s="0" t="n">
+      <c r="E50" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E51" s="0" t="n">
+      <c r="E51" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="2" t="n">
         <v>2.46100224548177</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E52" s="0" t="n">
+      <c r="E52" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="2" t="n">
         <v>5.86699775451993</v>
       </c>
-      <c r="D53" s="0" t="n">
+      <c r="D53" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E53" s="0" t="n">
+      <c r="E53" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="0" t="n">
+      <c r="C54" s="2" t="n">
         <v>5.86699775451867</v>
       </c>
-      <c r="D54" s="0" t="n">
+      <c r="D54" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E54" s="0" t="n">
+      <c r="E54" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="2" t="n">
         <v>13.4646321545165</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E55" s="0" t="n">
+      <c r="E55" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="2" t="n">
         <v>12.5985201545121</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E56" s="0" t="n">
+      <c r="E56" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="2" t="n">
         <v>0.66903724054699</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E57" s="0" t="n">
+      <c r="E57" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="0" t="n">
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E58" s="0" t="n">
+      <c r="E58" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="2" t="n">
         <v>9.06882563036854</v>
       </c>
-      <c r="D59" s="0" t="n">
+      <c r="D59" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E59" s="0" t="n">
+      <c r="E59" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="2" t="n">
         <v>8.32806553390242E-010</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E60" s="0" t="n">
+      <c r="E60" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61" s="2" t="n">
         <v>6.17128273476136</v>
       </c>
-      <c r="D61" s="0" t="n">
+      <c r="D61" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E61" s="0" t="n">
+      <c r="E61" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="2" t="n">
         <v>6.17128273392855</v>
       </c>
-      <c r="D62" s="0" t="n">
+      <c r="D62" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="2" t="n">
         <v>2.39854224464884</v>
       </c>
-      <c r="D63" s="0" t="n">
+      <c r="D63" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E63" s="0" t="n">
+      <c r="E63" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="2" t="n">
         <v>3.77274048927972</v>
       </c>
-      <c r="D64" s="0" t="n">
+      <c r="D64" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E64" s="0" t="n">
+      <c r="E64" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="2" t="n">
         <v>1.98380784464243</v>
       </c>
-      <c r="D65" s="0" t="n">
+      <c r="D65" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E65" s="0" t="n">
+      <c r="E65" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="2" t="n">
         <v>1.78893264463728</v>
       </c>
-      <c r="D66" s="0" t="n">
+      <c r="D66" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E66" s="0" t="n">
+      <c r="E66" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="2" t="n">
         <v>3.54566882267735</v>
       </c>
-      <c r="D67" s="0" t="n">
+      <c r="D67" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E67" s="0" t="n">
+      <c r="E67" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C68" s="0" t="n">
+      <c r="C68" s="2" t="n">
         <v>0.358920308694773</v>
       </c>
-      <c r="D68" s="0" t="n">
+      <c r="D68" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E68" s="0" t="n">
+      <c r="E68" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="2" t="n">
         <v>4.56832926881669</v>
       </c>
-      <c r="D69" s="0" t="n">
+      <c r="D69" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E69" s="0" t="n">
+      <c r="E69" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70" s="2" t="n">
         <v>4.56611882725672</v>
       </c>
-      <c r="D70" s="0" t="n">
+      <c r="D70" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E70" s="0" t="n">
+      <c r="E70" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="2" t="n">
         <v>3.87489482726835</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E71" s="0" t="n">
+      <c r="E71" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C72" s="0" t="n">
+      <c r="C72" s="2" t="n">
         <v>3.87710526881689</v>
       </c>
-      <c r="D72" s="0" t="n">
+      <c r="D72" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E72" s="0" t="n">
+      <c r="E72" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="2" t="n">
         <v>3.87710526881689</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E73" s="0" t="n">
+      <c r="E73" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C74" s="0" t="n">
+      <c r="C74" s="2" t="n">
         <v>2.22770555484157</v>
       </c>
-      <c r="D74" s="0" t="n">
+      <c r="D74" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E74" s="0" t="n">
+      <c r="E74" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75" s="2" t="n">
         <v>1.65161015552924</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E75" s="0" t="n">
+      <c r="E75" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76" s="2" t="n">
         <v>0.00221044155118574</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E76" s="0" t="n">
+      <c r="E76" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C77" s="0" t="n">
+      <c r="C77" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="D77" s="0" t="n">
+      <c r="D77" s="2" t="n">
         <v>0.4924</v>
       </c>
-      <c r="E77" s="0" t="n">
+      <c r="E77" s="2" t="n">
         <v>8.328</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="0" t="n">
+      <c r="C78" s="2" t="n">
         <v>-1.96893851242381E-008</v>
       </c>
-      <c r="D78" s="0" t="n">
+      <c r="D78" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E78" s="0" t="n">
+      <c r="E78" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E79" s="0" t="n">
+      <c r="E79" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="2" t="n">
         <v>-1.969</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E80" s="0" t="n">
+      <c r="E80" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C81" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="0" t="n">
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E81" s="0" t="n">
+      <c r="E81" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C82" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="0" t="n">
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E82" s="0" t="n">
+      <c r="E82" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="0" t="n">
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E83" s="0" t="n">
+      <c r="E83" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C84" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="0" t="n">
+      <c r="C84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E84" s="0" t="n">
+      <c r="E84" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="0" t="n">
+      <c r="C85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E85" s="0" t="n">
+      <c r="E85" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C86" s="0" t="n">
+      <c r="C86" s="2" t="n">
         <v>1.96894647401262E-008</v>
       </c>
-      <c r="D86" s="0" t="n">
+      <c r="D86" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E86" s="0" t="n">
+      <c r="E86" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C87" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="0" t="n">
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E87" s="0" t="n">
+      <c r="E87" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C88" s="0" t="n">
+      <c r="C88" s="2" t="n">
         <v>1.36848556311592</v>
       </c>
-      <c r="D88" s="0" t="n">
+      <c r="D88" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E88" s="0" t="n">
+      <c r="E88" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="0" t="n">
+      <c r="C89" s="2" t="n">
         <v>1.54745030046413</v>
       </c>
-      <c r="D89" s="0" t="n">
+      <c r="D89" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E89" s="0" t="n">
+      <c r="E89" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="0" t="n">
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E90" s="0" t="n">
+      <c r="E90" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91" s="2" t="n">
         <v>1.547450300464</v>
       </c>
-      <c r="D91" s="0" t="n">
+      <c r="D91" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E91" s="0" t="n">
+      <c r="E91" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="2" t="n">
         <v>1.54745030046383</v>
       </c>
-      <c r="D92" s="0" t="n">
+      <c r="D92" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E92" s="0" t="n">
+      <c r="E92" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C93" s="0" t="n">
+      <c r="C93" s="2" t="n">
         <v>3.30852390046624</v>
       </c>
-      <c r="D93" s="0" t="n">
+      <c r="D93" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E93" s="0" t="n">
+      <c r="E93" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C94" s="0" t="n">
+      <c r="C94" s="2" t="n">
         <v>3.04152750046578</v>
       </c>
-      <c r="D94" s="0" t="n">
+      <c r="D94" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E94" s="0" t="n">
+      <c r="E94" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C95" s="0" t="n">
+      <c r="C95" s="2" t="n">
         <v>3.35734279356104</v>
       </c>
-      <c r="D95" s="0" t="n">
+      <c r="D95" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E95" s="0" t="n">
+      <c r="E95" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C96" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="0" t="n">
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E96" s="0" t="n">
+      <c r="E96" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C97" s="0" t="n">
+      <c r="C97" s="2" t="n">
         <v>2.9426983501447</v>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E97" s="0" t="n">
+      <c r="E97" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C98" s="0" t="n">
+      <c r="C98" s="2" t="n">
         <v>0.172972130865029</v>
       </c>
-      <c r="D98" s="0" t="n">
+      <c r="D98" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E98" s="0" t="n">
+      <c r="E98" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C99" s="0" t="n">
+      <c r="C99" s="2" t="n">
         <v>0.591653936883625</v>
       </c>
-      <c r="D99" s="0" t="n">
+      <c r="D99" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E99" s="0" t="n">
+      <c r="E99" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C100" s="0" t="n">
+      <c r="C100" s="2" t="n">
         <v>0.418681806018596</v>
       </c>
-      <c r="D100" s="0" t="n">
+      <c r="D100" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E100" s="0" t="n">
+      <c r="E100" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C101" s="0" t="n">
+      <c r="C101" s="2" t="n">
         <v>0.227903068671968</v>
       </c>
-      <c r="D101" s="0" t="n">
+      <c r="D101" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E101" s="0" t="n">
+      <c r="E101" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C102" s="0" t="n">
+      <c r="C102" s="2" t="n">
         <v>0.190778737346628</v>
       </c>
-      <c r="D102" s="0" t="n">
+      <c r="D102" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E102" s="0" t="n">
+      <c r="E102" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C103" s="0" t="n">
+      <c r="C103" s="2" t="n">
         <v>0.132209668673607</v>
       </c>
-      <c r="D103" s="0" t="n">
+      <c r="D103" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E103" s="0" t="n">
+      <c r="E103" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C104" s="0" t="n">
+      <c r="C104" s="2" t="n">
         <v>0.0585690686730214</v>
       </c>
-      <c r="D104" s="0" t="n">
+      <c r="D104" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E104" s="0" t="n">
+      <c r="E104" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C105" s="0" t="n">
+      <c r="C105" s="2" t="n">
         <v>0.377386282380569</v>
       </c>
-      <c r="D105" s="0" t="n">
+      <c r="D105" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E105" s="0" t="n">
+      <c r="E105" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="s">
+      <c r="A106" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C106" s="0" t="n">
+      <c r="C106" s="2" t="n">
         <v>0.848949475475004</v>
       </c>
-      <c r="D106" s="0" t="n">
+      <c r="D106" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E106" s="0" t="n">
+      <c r="E106" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="2" t="n">
         <v>1.5209626722625</v>
       </c>
-      <c r="D107" s="0" t="n">
+      <c r="D107" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E107" s="0" t="n">
+      <c r="E107" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108" s="2" t="n">
         <v>0.496177414069656</v>
       </c>
-      <c r="D108" s="0" t="n">
+      <c r="D108" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E108" s="0" t="n">
+      <c r="E108" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109" s="2" t="n">
         <v>0.23607251406951</v>
       </c>
-      <c r="D109" s="0" t="n">
+      <c r="D109" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E109" s="0" t="n">
+      <c r="E109" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110" s="2" t="n">
         <v>1.26085777226327</v>
       </c>
-      <c r="D110" s="0" t="n">
+      <c r="D110" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E110" s="0" t="n">
+      <c r="E110" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111" s="2" t="n">
         <v>1.26085777226327</v>
       </c>
-      <c r="D111" s="0" t="n">
+      <c r="D111" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E111" s="0" t="n">
+      <c r="E111" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C112" s="0" t="n">
+      <c r="C112" s="2" t="n">
         <v>2.28511926535709</v>
       </c>
-      <c r="D112" s="0" t="n">
+      <c r="D112" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E112" s="0" t="n">
+      <c r="E112" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+      <c r="A113" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C113" s="0" t="n">
+      <c r="C113" s="2" t="n">
         <v>0.000523765099488657</v>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E113" s="0" t="n">
+      <c r="E113" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C114" s="0" t="n">
+      <c r="C114" s="2" t="n">
         <v>1.02478525819258</v>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E114" s="0" t="n">
+      <c r="E114" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C115" s="0" t="n">
+      <c r="C115" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="D115" s="0" t="n">
+      <c r="D115" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="E115" s="0" t="n">
+      <c r="E115" s="2" t="n">
         <v>1.969</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C116" s="0" t="n">
+      <c r="C116" s="2" t="n">
         <v>6.82701917999702</v>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E116" s="0" t="n">
+      <c r="E116" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="s">
+      <c r="A117" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C117" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="0" t="n">
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E117" s="0" t="n">
+      <c r="E117" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C118" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="0" t="n">
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E118" s="0" t="n">
+      <c r="E118" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C119" s="0" t="n">
+      <c r="C119" s="2" t="n">
         <v>-9.654</v>
       </c>
-      <c r="D119" s="0" t="n">
+      <c r="D119" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E119" s="0" t="n">
+      <c r="E119" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+      <c r="A120" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C120" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="0" t="n">
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E120" s="0" t="n">
+      <c r="E120" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C121" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="0" t="n">
+      <c r="C121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E121" s="0" t="n">
+      <c r="E121" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C122" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="0" t="n">
+      <c r="C122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E122" s="0" t="n">
+      <c r="E122" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C123" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="0" t="n">
+      <c r="C123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E123" s="0" t="n">
+      <c r="E123" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C124" s="0" t="n">
+      <c r="C124" s="2" t="n">
         <v>9.65373232000438E-008</v>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D124" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E124" s="0" t="n">
+      <c r="E124" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C125" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="0" t="n">
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E125" s="0" t="n">
+      <c r="E125" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C126" s="0" t="n">
+      <c r="C126" s="2" t="n">
         <v>5.69997032306891</v>
       </c>
-      <c r="D126" s="0" t="n">
+      <c r="D126" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E126" s="0" t="n">
+      <c r="E126" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C127" s="0" t="n">
+      <c r="C127" s="2" t="n">
         <v>7.05847700128102</v>
       </c>
-      <c r="D127" s="0" t="n">
+      <c r="D127" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E127" s="0" t="n">
+      <c r="E127" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="0" t="n">
+      <c r="C128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E128" s="0" t="n">
+      <c r="E128" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C129" s="0" t="n">
+      <c r="C129" s="2" t="n">
         <v>7.05847700128054</v>
       </c>
-      <c r="D129" s="0" t="n">
+      <c r="D129" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E129" s="0" t="n">
+      <c r="E129" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C130" s="0" t="n">
+      <c r="C130" s="2" t="n">
         <v>7.05847700128</v>
       </c>
-      <c r="D130" s="0" t="n">
+      <c r="D130" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E130" s="0" t="n">
+      <c r="E130" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="A131" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C131" s="2" t="n">
         <v>15.7103918012915</v>
       </c>
-      <c r="D131" s="0" t="n">
+      <c r="D131" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E131" s="0" t="n">
+      <c r="E131" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="s">
+      <c r="A132" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C132" s="0" t="n">
+      <c r="C132" s="2" t="n">
         <v>14.5577042012894</v>
       </c>
-      <c r="D132" s="0" t="n">
+      <c r="D132" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E132" s="0" t="n">
+      <c r="E132" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="s">
+      <c r="A133" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C133" s="0" t="n">
+      <c r="C133" s="2" t="n">
         <v>2.4873080978377</v>
       </c>
-      <c r="D133" s="0" t="n">
+      <c r="D133" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E133" s="0" t="n">
+      <c r="E133" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="s">
+      <c r="A134" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="0" t="n">
+      <c r="C134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E134" s="0" t="n">
+      <c r="E134" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="s">
+      <c r="A135" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C135" s="0" t="n">
+      <c r="C135" s="2" t="n">
         <v>11.2984642688082</v>
       </c>
-      <c r="D135" s="0" t="n">
+      <c r="D135" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E135" s="0" t="n">
+      <c r="E135" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="s">
+      <c r="A136" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C136" s="0" t="n">
+      <c r="C136" s="2" t="n">
         <v>1.08699105962718</v>
       </c>
-      <c r="D136" s="0" t="n">
+      <c r="D136" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E136" s="0" t="n">
+      <c r="E136" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="s">
+      <c r="A137" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C137" s="0" t="n">
+      <c r="C137" s="2" t="n">
         <v>3.91927527692857</v>
       </c>
-      <c r="D137" s="0" t="n">
+      <c r="D137" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E137" s="0" t="n">
+      <c r="E137" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="s">
+      <c r="A138" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C138" s="0" t="n">
+      <c r="C138" s="2" t="n">
         <v>2.83228421730139</v>
       </c>
-      <c r="D138" s="0" t="n">
+      <c r="D138" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E138" s="0" t="n">
+      <c r="E138" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="s">
+      <c r="A139" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C139" s="0" t="n">
+      <c r="C139" s="2" t="n">
         <v>1.42743833909665</v>
       </c>
-      <c r="D139" s="0" t="n">
+      <c r="D139" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E139" s="0" t="n">
+      <c r="E139" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="s">
+      <c r="A140" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C140" s="0" t="n">
+      <c r="C140" s="2" t="n">
         <v>1.40484587820474</v>
       </c>
-      <c r="D140" s="0" t="n">
+      <c r="D140" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E140" s="0" t="n">
+      <c r="E140" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="s">
+      <c r="A141" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B141" s="0" t="s">
+      <c r="B141" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C141" s="0" t="n">
+      <c r="C141" s="2" t="n">
         <v>0.820201739103642</v>
       </c>
-      <c r="D141" s="0" t="n">
+      <c r="D141" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E141" s="0" t="n">
+      <c r="E141" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="s">
+      <c r="A142" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C142" s="0" t="n">
+      <c r="C142" s="2" t="n">
         <v>0.584644139101096</v>
       </c>
-      <c r="D142" s="0" t="n">
+      <c r="D142" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E142" s="0" t="n">
+      <c r="E142" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
+      <c r="A143" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B143" s="0" t="s">
+      <c r="B143" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C143" s="0" t="n">
+      <c r="C143" s="2" t="n">
         <v>2.45333132924989</v>
       </c>
-      <c r="D143" s="0" t="n">
+      <c r="D143" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E143" s="0" t="n">
+      <c r="E143" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="s">
+      <c r="A144" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="B144" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C144" s="0" t="n">
+      <c r="C144" s="2" t="n">
         <v>0.540874025794242</v>
       </c>
-      <c r="D144" s="0" t="n">
+      <c r="D144" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E144" s="0" t="n">
+      <c r="E144" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="s">
+      <c r="A145" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B145" s="0" t="s">
+      <c r="B145" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C145" s="0" t="n">
+      <c r="C145" s="2" t="n">
         <v>2.97797128784429</v>
       </c>
-      <c r="D145" s="0" t="n">
+      <c r="D145" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E145" s="0" t="n">
+      <c r="E145" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
+      <c r="A146" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C146" s="0" t="n">
+      <c r="C146" s="2" t="n">
         <v>2.97797128687757</v>
       </c>
-      <c r="D146" s="0" t="n">
+      <c r="D146" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E146" s="0" t="n">
+      <c r="E146" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="s">
+      <c r="A147" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>2.97797128687757</v>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>9.654</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B147" s="0" t="s">
+      <c r="B148" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C147" s="0" t="n">
+      <c r="C148" s="2" t="n">
         <v>2.13807328687711</v>
       </c>
-      <c r="D147" s="0" t="n">
+      <c r="D148" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E147" s="0" t="n">
+      <c r="E148" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="s">
+    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B148" s="0" t="s">
+      <c r="B149" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C148" s="0" t="n">
+      <c r="C149" s="2" t="n">
         <v>2.13807328784816</v>
       </c>
-      <c r="D148" s="0" t="n">
+      <c r="D149" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E148" s="0" t="n">
+      <c r="E149" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="s">
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B150" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C149" s="0" t="n">
+      <c r="C150" s="2" t="n">
         <v>2.13807328784816</v>
       </c>
-      <c r="D149" s="0" t="n">
+      <c r="D150" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E149" s="0" t="n">
+      <c r="E150" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="s">
+    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>2.13807338438951</v>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>9.654</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B150" s="0" t="s">
+      <c r="B152" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C150" s="0" t="n">
+      <c r="C152" s="2" t="n">
         <v>2.13807338438951</v>
       </c>
-      <c r="D150" s="0" t="n">
+      <c r="D152" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E150" s="0" t="n">
+      <c r="E152" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="s">
+    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B151" s="0" t="s">
+      <c r="B153" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C151" s="0" t="n">
+      <c r="C153" s="2" t="n">
         <v>-9.55724246626087E-008</v>
       </c>
-      <c r="D151" s="0" t="n">
+      <c r="D153" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E151" s="0" t="n">
+      <c r="E153" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="s">
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B152" s="0" t="s">
+      <c r="B154" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C152" s="0" t="n">
+      <c r="C154" s="2" t="n">
         <v>9.65403838355527E-010</v>
       </c>
-      <c r="D152" s="0" t="n">
+      <c r="D154" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E152" s="0" t="n">
+      <c r="E154" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="s">
+    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B153" s="0" t="s">
+      <c r="B155" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C153" s="0" t="n">
+      <c r="C155" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="D153" s="0" t="n">
+      <c r="D155" s="2" t="n">
         <v>0.65</v>
       </c>
-      <c r="E153" s="0" t="n">
+      <c r="E155" s="2" t="n">
         <v>9.654</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="s">
+    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B154" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C154" s="0" t="n">
+      <c r="B156" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C156" s="2" t="n">
         <v>0.5970002640036</v>
       </c>
-      <c r="D154" s="0" t="n">
+      <c r="D156" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E154" s="0" t="n">
+      <c r="E156" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="s">
+    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B155" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C155" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="0" t="n">
+      <c r="B157" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E155" s="0" t="n">
+      <c r="E157" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="s">
+    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B156" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C156" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D156" s="0" t="n">
+      <c r="B158" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E156" s="0" t="n">
+      <c r="E158" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="s">
+    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B157" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C157" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" s="0" t="n">
+      <c r="B159" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E157" s="0" t="n">
+      <c r="E159" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="s">
+    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B158" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C158" s="0" t="n">
+      <c r="B160" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C160" s="2" t="n">
         <v>-4.94483364720653</v>
       </c>
-      <c r="D158" s="0" t="n">
+      <c r="D160" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E158" s="0" t="n">
+      <c r="E160" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="s">
+    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B159" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C159" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="0" t="n">
+      <c r="B161" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E159" s="0" t="n">
+      <c r="E161" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="s">
+    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B160" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C160" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="0" t="n">
+      <c r="B162" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E160" s="0" t="n">
+      <c r="E162" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="s">
+    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B161" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C161" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="0" t="n">
+      <c r="B163" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E161" s="0" t="n">
+      <c r="E163" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="s">
+    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B162" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C162" s="0" t="n">
+      <c r="B164" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C164" s="2" t="n">
         <v>1.01356844181818E-007</v>
       </c>
-      <c r="D162" s="0" t="n">
+      <c r="D164" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E162" s="0" t="n">
+      <c r="E164" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="s">
+    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B163" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C163" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D163" s="0" t="n">
+      <c r="B165" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E163" s="0" t="n">
+      <c r="E165" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="s">
+    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B164" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C164" s="0" t="n">
+      <c r="B166" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C166" s="2" t="n">
         <v>-3.4494032742613</v>
       </c>
-      <c r="D164" s="0" t="n">
+      <c r="D166" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E164" s="0" t="n">
+      <c r="E166" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="s">
+    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B165" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C165" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" s="0" t="n">
+      <c r="B167" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E165" s="0" t="n">
+      <c r="E167" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="s">
+    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B166" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C166" s="0" t="n">
+      <c r="B168" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C168" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="D166" s="0" t="n">
+      <c r="D168" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E166" s="0" t="n">
+      <c r="E168" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="s">
+    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B167" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C167" s="0" t="n">
+      <c r="B169" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C169" s="2" t="n">
         <v>-1.49569866025825</v>
       </c>
-      <c r="D167" s="0" t="n">
+      <c r="D169" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E167" s="0" t="n">
+      <c r="E169" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="s">
+    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B168" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C168" s="0" t="n">
+      <c r="B170" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C170" s="2" t="n">
         <v>8.64030133974072</v>
       </c>
-      <c r="D168" s="0" t="n">
+      <c r="D170" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E168" s="0" t="n">
+      <c r="E170" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0" t="s">
+    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B169" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C169" s="0" t="n">
+      <c r="B171" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C171" s="2" t="n">
         <v>8.01288293972952</v>
       </c>
-      <c r="D169" s="0" t="n">
+      <c r="D171" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E169" s="0" t="n">
+      <c r="E171" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="s">
+    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B170" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C170" s="0" t="n">
+      <c r="B172" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C172" s="2" t="n">
         <v>7.25876453972736</v>
       </c>
-      <c r="D170" s="0" t="n">
+      <c r="D172" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E170" s="0" t="n">
+      <c r="E172" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0" t="s">
+    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B171" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C171" s="0" t="n">
+      <c r="B173" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C173" s="2" t="n">
         <v>5.50726384108792</v>
       </c>
-      <c r="D171" s="0" t="n">
+      <c r="D173" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E171" s="0" t="n">
+      <c r="E173" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0" t="s">
+    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B172" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C172" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D172" s="0" t="n">
+      <c r="B174" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E172" s="0" t="n">
+      <c r="E174" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="s">
+    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B173" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C173" s="0" t="n">
+      <c r="B175" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C175" s="2" t="n">
         <v>4.09773589126472</v>
       </c>
-      <c r="D173" s="0" t="n">
+      <c r="D175" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E173" s="0" t="n">
+      <c r="E175" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0" t="s">
+    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B174" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C174" s="0" t="n">
+      <c r="B176" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C176" s="2" t="n">
         <v>0.0145803532454725</v>
       </c>
-      <c r="D174" s="0" t="n">
+      <c r="D176" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E174" s="0" t="n">
+      <c r="E176" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0" t="s">
+    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B175" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C175" s="0" t="n">
+      <c r="B177" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C177" s="2" t="n">
         <v>3.42609047425694</v>
       </c>
-      <c r="D175" s="0" t="n">
+      <c r="D177" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E175" s="0" t="n">
+      <c r="E177" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0" t="s">
+    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B176" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C176" s="0" t="n">
+      <c r="B178" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C178" s="2" t="n">
         <v>3.41151012101147</v>
       </c>
-      <c r="D176" s="0" t="n">
+      <c r="D178" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E176" s="0" t="n">
+      <c r="E178" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0" t="s">
+    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B177" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C177" s="0" t="n">
+      <c r="B179" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C179" s="2" t="n">
         <v>1.42638390700087</v>
       </c>
-      <c r="D177" s="0" t="n">
+      <c r="D179" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E177" s="0" t="n">
+      <c r="E179" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0" t="s">
+    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B178" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C178" s="0" t="n">
+      <c r="B180" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C180" s="2" t="n">
         <v>1.98512621401061</v>
       </c>
-      <c r="D178" s="0" t="n">
+      <c r="D180" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E178" s="0" t="n">
+      <c r="E180" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0" t="s">
+    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B179" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C179" s="0" t="n">
+      <c r="B181" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C181" s="2" t="n">
         <v>1.08074630700558</v>
       </c>
-      <c r="D179" s="0" t="n">
+      <c r="D181" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E179" s="0" t="n">
+      <c r="E181" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0" t="s">
+    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B180" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C180" s="0" t="n">
+      <c r="B182" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C182" s="2" t="n">
         <v>0.904379907005026</v>
       </c>
-      <c r="D180" s="0" t="n">
+      <c r="D182" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E180" s="0" t="n">
+      <c r="E182" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0" t="s">
+    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B181" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C181" s="0" t="n">
+      <c r="B183" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C183" s="2" t="n">
         <v>1.37646859829537</v>
       </c>
-      <c r="D181" s="0" t="n">
+      <c r="D183" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E181" s="0" t="n">
+      <c r="E183" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0" t="s">
+    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B182" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C182" s="0" t="n">
+      <c r="B184" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C184" s="2" t="n">
         <v>-1.00351801047623E-007</v>
       </c>
-      <c r="D182" s="0" t="n">
+      <c r="D184" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E182" s="0" t="n">
+      <c r="E184" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0" t="s">
+    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B183" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C183" s="0" t="n">
+      <c r="B185" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C185" s="2" t="n">
         <v>2.46483642625575</v>
       </c>
-      <c r="D183" s="0" t="n">
+      <c r="D185" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E183" s="0" t="n">
+      <c r="E185" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0" t="s">
+    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B184" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C184" s="0" t="n">
+      <c r="B186" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C186" s="2" t="n">
         <v>2.46483642522684</v>
       </c>
-      <c r="D184" s="0" t="n">
+      <c r="D186" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E184" s="0" t="n">
+      <c r="E186" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0" t="s">
+    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B185" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C185" s="0" t="n">
+      <c r="B187" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C187" s="2" t="n">
         <v>1.84045882523313</v>
       </c>
-      <c r="D185" s="0" t="n">
+      <c r="D187" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E185" s="0" t="n">
+      <c r="E187" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="s">
+    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B186" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C186" s="0" t="n">
+      <c r="B188" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C188" s="2" t="n">
         <v>1.84045882625222</v>
       </c>
-      <c r="D186" s="0" t="n">
+      <c r="D188" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E186" s="0" t="n">
+      <c r="E188" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="s">
+    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B187" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C187" s="0" t="n">
+      <c r="B189" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C189" s="2" t="n">
         <v>1.84045882625222</v>
       </c>
-      <c r="D187" s="0" t="n">
+      <c r="D189" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E187" s="0" t="n">
+      <c r="E189" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="s">
+    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B188" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C188" s="0" t="n">
+      <c r="B190" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C190" s="2" t="n">
         <v>1.84045892761101</v>
       </c>
-      <c r="D188" s="0" t="n">
+      <c r="D190" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E188" s="0" t="n">
+      <c r="E190" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="s">
+    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B189" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C189" s="0" t="n">
+      <c r="B191" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C191" s="2" t="n">
         <v>-1.00346253771013E-007</v>
       </c>
-      <c r="D189" s="0" t="n">
+      <c r="D191" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E189" s="0" t="n">
+      <c r="E191" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0" t="s">
+    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B190" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C190" s="0" t="n">
+      <c r="B192" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C192" s="2" t="n">
         <v>1.01360623487601E-009</v>
       </c>
-      <c r="D190" s="0" t="n">
+      <c r="D192" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E190" s="0" t="n">
+      <c r="E192" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0" t="s">
+    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B191" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C191" s="0" t="n">
+      <c r="B193" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C193" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="D191" s="0" t="n">
+      <c r="D193" s="2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E191" s="0" t="n">
+      <c r="E193" s="2" t="n">
         <v>4.9448</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0" t="s">
+    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B192" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C192" s="0" t="n">
+      <c r="B194" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C194" s="2" t="n">
         <v>5.00398239363803</v>
       </c>
-      <c r="D192" s="0" t="n">
+      <c r="D194" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E192" s="0" t="n">
+      <c r="E194" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0" t="s">
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B193" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C193" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="0" t="n">
+      <c r="B195" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E193" s="0" t="n">
+      <c r="E195" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="s">
+    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B194" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C194" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" s="0" t="n">
+      <c r="B196" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E194" s="0" t="n">
+      <c r="E196" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="s">
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B195" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C195" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D195" s="0" t="n">
+      <c r="B197" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E195" s="0" t="n">
+      <c r="E197" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0" t="s">
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B196" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C196" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D196" s="0" t="n">
+      <c r="B198" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E196" s="0" t="n">
+      <c r="E198" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0" t="s">
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B197" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C197" s="0" t="n">
+      <c r="B199" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C199" s="2" t="n">
         <v>-7.28392319195215</v>
       </c>
-      <c r="D197" s="0" t="n">
+      <c r="D199" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E197" s="0" t="n">
+      <c r="E199" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0" t="s">
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B198" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C198" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D198" s="0" t="n">
+      <c r="B200" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E198" s="0" t="n">
+      <c r="E200" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="0" t="s">
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B199" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C199" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D199" s="0" t="n">
+      <c r="B201" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E199" s="0" t="n">
+      <c r="E201" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="0" t="s">
+    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B200" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C200" s="0" t="n">
+      <c r="B202" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C202" s="2" t="n">
         <v>7.28367733438014E-008</v>
       </c>
-      <c r="D200" s="0" t="n">
+      <c r="D202" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E200" s="0" t="n">
+      <c r="E202" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="0" t="s">
+    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B201" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C201" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D201" s="0" t="n">
+      <c r="B203" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C203" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E201" s="0" t="n">
+      <c r="E203" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="0" t="s">
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B202" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C202" s="0" t="n">
+      <c r="B204" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C204" s="2" t="n">
         <v>-0.0313209425602704</v>
       </c>
-      <c r="D202" s="0" t="n">
+      <c r="D204" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E202" s="0" t="n">
+      <c r="E204" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="0" t="s">
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B203" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C203" s="0" t="n">
+      <c r="B205" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C205" s="2" t="n">
         <v>0.486919226529752</v>
       </c>
-      <c r="D203" s="0" t="n">
+      <c r="D205" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E203" s="0" t="n">
+      <c r="E205" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="0" t="s">
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B204" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C204" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D204" s="0" t="n">
+      <c r="B206" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C206" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E204" s="0" t="n">
+      <c r="E206" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="0" t="s">
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B205" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C205" s="0" t="n">
+      <c r="B207" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C207" s="2" t="n">
         <v>0.48691922653428</v>
       </c>
-      <c r="D205" s="0" t="n">
+      <c r="D207" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E205" s="0" t="n">
+      <c r="E207" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="0" t="s">
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B206" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C206" s="0" t="n">
+      <c r="B208" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C208" s="2" t="n">
         <v>0.486919226522254</v>
       </c>
-      <c r="D206" s="0" t="n">
+      <c r="D208" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E206" s="0" t="n">
+      <c r="E208" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="0" t="s">
+    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B207" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C207" s="0" t="n">
+      <c r="B209" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C209" s="2" t="n">
         <v>6.89458645850349</v>
       </c>
-      <c r="D207" s="0" t="n">
+      <c r="D209" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E207" s="0" t="n">
+      <c r="E209" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="0" t="s">
+    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B208" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C208" s="0" t="n">
+      <c r="B210" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C210" s="2" t="n">
         <v>5.87338042698286</v>
       </c>
-      <c r="D208" s="0" t="n">
+      <c r="D210" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E208" s="0" t="n">
+      <c r="E210" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="0" t="s">
+    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B209" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C209" s="0" t="n">
+      <c r="B211" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C211" s="2" t="n">
         <v>3.46458717234597</v>
       </c>
-      <c r="D209" s="0" t="n">
+      <c r="D211" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E209" s="0" t="n">
+      <c r="E211" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="0" t="s">
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B210" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C210" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D210" s="0" t="n">
+      <c r="B212" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E210" s="0" t="n">
+      <c r="E212" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="0" t="s">
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B211" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C211" s="0" t="n">
+      <c r="B213" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C213" s="2" t="n">
         <v>7.50554196523136</v>
       </c>
-      <c r="D211" s="0" t="n">
+      <c r="D213" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E211" s="0" t="n">
+      <c r="E213" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="0" t="s">
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B212" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C212" s="0" t="n">
+      <c r="B214" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C214" s="2" t="n">
         <v>5.81896066181984</v>
       </c>
-      <c r="D212" s="0" t="n">
+      <c r="D214" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E212" s="0" t="n">
+      <c r="E214" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="0" t="s">
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B213" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C213" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D213" s="0" t="n">
+      <c r="B215" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E213" s="0" t="n">
+      <c r="E215" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="0" t="s">
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B214" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C214" s="0" t="n">
+      <c r="B216" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C216" s="2" t="n">
         <v>1.4649626029673</v>
       </c>
-      <c r="D214" s="0" t="n">
+      <c r="D216" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E214" s="0" t="n">
+      <c r="E216" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="0" t="s">
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B215" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C215" s="0" t="n">
+      <c r="B217" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C217" s="2" t="n">
         <v>0.90520407168297</v>
       </c>
-      <c r="D215" s="0" t="n">
+      <c r="D217" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E215" s="0" t="n">
+      <c r="E217" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="0" t="s">
+    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B216" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C216" s="0" t="n">
+      <c r="B218" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C218" s="2" t="n">
         <v>0.559758531284334</v>
       </c>
-      <c r="D216" s="0" t="n">
+      <c r="D218" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E216" s="0" t="n">
+      <c r="E218" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="0" t="s">
+    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B217" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C217" s="0" t="n">
+      <c r="B219" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C219" s="2" t="n">
         <v>0.388773917352602</v>
       </c>
-      <c r="D217" s="0" t="n">
+      <c r="D219" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E217" s="0" t="n">
+      <c r="E219" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="0" t="s">
+    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B218" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C218" s="0" t="n">
+      <c r="B220" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C220" s="2" t="n">
         <v>0.170984613931732</v>
       </c>
-      <c r="D218" s="0" t="n">
+      <c r="D220" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E218" s="0" t="n">
+      <c r="E220" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="0" t="s">
+    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B219" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C219" s="0" t="n">
+      <c r="B221" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C221" s="2" t="n">
         <v>1.94335049055655</v>
       </c>
-      <c r="D219" s="0" t="n">
+      <c r="D221" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E219" s="0" t="n">
+      <c r="E221" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="0" t="s">
+    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B220" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C220" s="0" t="n">
+      <c r="B222" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C222" s="2" t="n">
         <v>-7.21108082103383E-008</v>
       </c>
-      <c r="D220" s="0" t="n">
+      <c r="D222" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E220" s="0" t="n">
+      <c r="E222" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="0" t="s">
+    <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B221" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C221" s="0" t="n">
+      <c r="B223" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C223" s="2" t="n">
         <v>1.15403370824295</v>
       </c>
-      <c r="D221" s="0" t="n">
+      <c r="D223" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E221" s="0" t="n">
+      <c r="E223" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="0" t="s">
+    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B222" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C222" s="0" t="n">
+      <c r="B224" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C224" s="2" t="n">
         <v>1.15403363541346</v>
       </c>
-      <c r="D222" s="0" t="n">
+      <c r="D224" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E222" s="0" t="n">
+      <c r="E224" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="0" t="s">
+    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B223" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C223" s="0" t="n">
+      <c r="B225" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C225" s="2" t="n">
         <v>0.182358281607563</v>
       </c>
-      <c r="D223" s="0" t="n">
+      <c r="D225" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E223" s="0" t="n">
+      <c r="E225" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="0" t="s">
+    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B224" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C224" s="0" t="n">
+      <c r="B226" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C226" s="2" t="n">
         <v>0.182358354440685</v>
       </c>
-      <c r="D224" s="0" t="n">
+      <c r="D226" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E224" s="0" t="n">
+      <c r="E226" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="0" t="s">
+    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B225" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C225" s="0" t="n">
+      <c r="B227" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C227" s="2" t="n">
         <v>0.182358354440685</v>
       </c>
-      <c r="D225" s="0" t="n">
+      <c r="D227" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E225" s="0" t="n">
+      <c r="E227" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="0" t="s">
+    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B226" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C226" s="0" t="n">
+      <c r="B228" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C228" s="2" t="n">
         <v>0.182358499389938</v>
       </c>
-      <c r="D226" s="0" t="n">
+      <c r="D228" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E226" s="0" t="n">
+      <c r="E228" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="0" t="s">
+    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B227" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C227" s="0" t="n">
+      <c r="B229" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C229" s="2" t="n">
         <v>-7.21058375475826E-008</v>
       </c>
-      <c r="D227" s="0" t="n">
+      <c r="D229" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E227" s="0" t="n">
+      <c r="E229" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="0" t="s">
+    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B228" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C228" s="0" t="n">
+      <c r="B230" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C230" s="2" t="n">
         <v>7.28400134187598E-008</v>
       </c>
-      <c r="D228" s="0" t="n">
+      <c r="D230" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E228" s="0" t="n">
+      <c r="E230" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="0" t="s">
+    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B229" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C229" s="0" t="n">
+      <c r="B231" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C231" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="D229" s="0" t="n">
+      <c r="D231" s="2" t="n">
         <v>0.59</v>
       </c>
-      <c r="E229" s="0" t="n">
+      <c r="E231" s="2" t="n">
         <v>7.2839</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="0" t="s">
+    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B230" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C230" s="0" t="n">
+      <c r="B232" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C232" s="2" t="n">
         <v>11.9139097200115</v>
       </c>
-      <c r="D230" s="0" t="n">
+      <c r="D232" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E230" s="0" t="n">
+      <c r="E232" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="0" t="s">
+    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B231" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C231" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D231" s="0" t="n">
+      <c r="B233" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C233" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E231" s="0" t="n">
+      <c r="E233" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="0" t="s">
+    <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B232" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C232" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D232" s="0" t="n">
+      <c r="B234" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C234" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E232" s="0" t="n">
+      <c r="E234" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="0" t="s">
+    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B233" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C233" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D233" s="0" t="n">
+      <c r="B235" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E233" s="0" t="n">
+      <c r="E235" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="0" t="s">
+    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B234" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C234" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D234" s="0" t="n">
+      <c r="B236" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E234" s="0" t="n">
+      <c r="E236" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="0" t="s">
+    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B235" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C235" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D235" s="0" t="n">
+      <c r="B237" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C237" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E235" s="0" t="n">
+      <c r="E237" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="0" t="s">
+    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B236" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C236" s="0" t="n">
+      <c r="B238" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C238" s="2" t="n">
         <v>-26.714</v>
       </c>
-      <c r="D236" s="0" t="n">
+      <c r="D238" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E236" s="0" t="n">
+      <c r="E238" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="0" t="s">
+    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B237" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C237" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D237" s="0" t="n">
+      <c r="B239" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E237" s="0" t="n">
+      <c r="E239" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="0" t="s">
+    <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A240" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B238" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C238" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D238" s="0" t="n">
+      <c r="B240" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C240" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E238" s="0" t="n">
+      <c r="E240" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="0" t="s">
+    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A241" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B239" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C239" s="0" t="n">
+      <c r="B241" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C241" s="2" t="n">
         <v>-1.15701005397392</v>
       </c>
-      <c r="D239" s="0" t="n">
+      <c r="D241" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E239" s="0" t="n">
+      <c r="E241" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="0" t="s">
+    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A242" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B240" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C240" s="0" t="n">
+      <c r="B242" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C242" s="2" t="n">
         <v>-0.898172808115418</v>
       </c>
-      <c r="D240" s="0" t="n">
+      <c r="D242" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E240" s="0" t="n">
+      <c r="E242" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="0" t="s">
+    <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B241" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C241" s="0" t="n">
+      <c r="B243" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C243" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D241" s="0" t="n">
+      <c r="D243" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E241" s="0" t="n">
+      <c r="E243" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="0" t="s">
+    <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A244" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B242" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C242" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D242" s="0" t="n">
+      <c r="B244" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C244" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E242" s="0" t="n">
+      <c r="E244" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="0" t="s">
+    <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A245" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B243" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C243" s="0" t="n">
+      <c r="B245" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C245" s="2" t="n">
         <v>-0.587011671166972</v>
       </c>
-      <c r="D243" s="0" t="n">
+      <c r="D245" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E243" s="0" t="n">
+      <c r="E245" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="0" t="s">
+    <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A246" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B244" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C244" s="0" t="n">
+      <c r="B246" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C246" s="2" t="n">
         <v>-0.58701167113178</v>
       </c>
-      <c r="D244" s="0" t="n">
+      <c r="D246" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E244" s="0" t="n">
+      <c r="E246" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="0" t="s">
+    <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A247" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B245" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C245" s="0" t="n">
+      <c r="B247" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C247" s="2" t="n">
         <v>-1.12930587115859</v>
       </c>
-      <c r="D245" s="0" t="n">
+      <c r="D247" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E245" s="0" t="n">
+      <c r="E247" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="0" t="s">
+    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B246" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C246" s="0" t="n">
+      <c r="B248" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C248" s="2" t="n">
         <v>-1.78914167115472</v>
       </c>
-      <c r="D246" s="0" t="n">
+      <c r="D248" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E246" s="0" t="n">
+      <c r="E248" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="0" t="s">
+    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A249" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B247" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C247" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D247" s="0" t="n">
+      <c r="B249" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C249" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E247" s="0" t="n">
+      <c r="E249" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="0" t="s">
+    <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A250" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B248" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C248" s="0" t="n">
+      <c r="B250" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C250" s="2" t="n">
         <v>3.45038413403387</v>
       </c>
-      <c r="D248" s="0" t="n">
+      <c r="D250" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E248" s="0" t="n">
+      <c r="E250" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="0" t="s">
+    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B249" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C249" s="0" t="n">
+      <c r="B251" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C251" s="2" t="n">
         <v>21.0173942415587</v>
       </c>
-      <c r="D249" s="0" t="n">
+      <c r="D251" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E249" s="0" t="n">
+      <c r="E251" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="0" t="s">
+    <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B250" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C250" s="0" t="n">
+      <c r="B252" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C252" s="2" t="n">
         <v>2.67142458845448E-009</v>
       </c>
-      <c r="D250" s="0" t="n">
+      <c r="D252" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E250" s="0" t="n">
+      <c r="E252" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="0" t="s">
+    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A253" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B251" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C251" s="0" t="n">
+      <c r="B253" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C253" s="2" t="n">
         <v>0.876801608134663</v>
       </c>
-      <c r="D251" s="0" t="n">
+      <c r="D253" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E251" s="0" t="n">
+      <c r="E253" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="0" t="s">
+    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A254" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B252" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C252" s="0" t="n">
+      <c r="B254" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C254" s="2" t="n">
         <v>0.876801605463239</v>
       </c>
-      <c r="D252" s="0" t="n">
+      <c r="D254" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E252" s="0" t="n">
+      <c r="E254" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="0" t="s">
+    <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A255" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B253" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C253" s="0" t="n">
+      <c r="B255" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C255" s="2" t="n">
         <v>0.538926468476706</v>
       </c>
-      <c r="D253" s="0" t="n">
+      <c r="D255" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E253" s="0" t="n">
+      <c r="E255" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="0" t="s">
+    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A256" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B254" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C254" s="0" t="n">
+      <c r="B256" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C256" s="2" t="n">
         <v>0.337875136986532</v>
       </c>
-      <c r="D254" s="0" t="n">
+      <c r="D256" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E254" s="0" t="n">
+      <c r="E256" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="0" t="s">
+    <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A257" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B255" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C255" s="0" t="n">
+      <c r="B257" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C257" s="2" t="n">
         <v>0.247743868498768</v>
       </c>
-      <c r="D255" s="0" t="n">
+      <c r="D257" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E255" s="0" t="n">
+      <c r="E257" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="0" t="s">
+    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A258" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B256" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C256" s="0" t="n">
+      <c r="B258" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C258" s="2" t="n">
         <v>0.0901312684877639</v>
       </c>
-      <c r="D256" s="0" t="n">
+      <c r="D258" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E256" s="0" t="n">
+      <c r="E258" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="0" t="s">
+    <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A259" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B257" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C257" s="0" t="n">
+      <c r="B259" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C259" s="2" t="n">
         <v>2.4894485851233</v>
       </c>
-      <c r="D257" s="0" t="n">
+      <c r="D259" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E257" s="0" t="n">
+      <c r="E259" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="0" t="s">
+    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A260" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B258" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C258" s="0" t="n">
+      <c r="B260" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C260" s="2" t="n">
         <v>1.16480252220645</v>
       </c>
-      <c r="D258" s="0" t="n">
+      <c r="D260" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E258" s="0" t="n">
+      <c r="E260" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="0" t="s">
+    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A261" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B259" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C259" s="0" t="n">
+      <c r="B261" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C261" s="2" t="n">
         <v>8.08192149040718</v>
       </c>
-      <c r="D259" s="0" t="n">
+      <c r="D261" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E259" s="0" t="n">
+      <c r="E261" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="0" t="s">
+    <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A262" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B260" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C260" s="0" t="n">
+      <c r="B262" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C262" s="2" t="n">
         <v>7.97932005922518</v>
       </c>
-      <c r="D260" s="0" t="n">
+      <c r="D262" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E260" s="0" t="n">
+      <c r="E262" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="0" t="s">
+    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A263" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B261" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C261" s="0" t="n">
+      <c r="B263" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C263" s="2" t="n">
         <v>7.41565465924942</v>
       </c>
-      <c r="D261" s="0" t="n">
+      <c r="D263" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E261" s="0" t="n">
+      <c r="E263" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="0" t="s">
+    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A264" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B262" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C262" s="0" t="n">
+      <c r="B264" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C264" s="2" t="n">
         <v>7.51825609040591</v>
       </c>
-      <c r="D262" s="0" t="n">
+      <c r="D264" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E262" s="0" t="n">
+      <c r="E264" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="0" t="s">
+    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A265" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B263" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C263" s="0" t="n">
+      <c r="B265" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C265" s="2" t="n">
         <v>7.51825609040591</v>
       </c>
-      <c r="D263" s="0" t="n">
+      <c r="D265" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E263" s="0" t="n">
+      <c r="E265" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="0" t="s">
+    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A266" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B264" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C264" s="0" t="n">
+      <c r="B266" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C266" s="2" t="n">
         <v>7.42779682749186</v>
       </c>
-      <c r="D264" s="0" t="n">
+      <c r="D266" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E264" s="0" t="n">
+      <c r="E266" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="0" t="s">
+    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A267" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B265" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C265" s="0" t="n">
+      <c r="B267" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C267" s="2" t="n">
         <v>0.193060694059714</v>
       </c>
-      <c r="D265" s="0" t="n">
+      <c r="D267" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E265" s="0" t="n">
+      <c r="E267" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="0" t="s">
+    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B266" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C266" s="0" t="n">
+      <c r="B268" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C268" s="2" t="n">
         <v>0.102601431162385</v>
       </c>
-      <c r="D266" s="0" t="n">
+      <c r="D268" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E266" s="0" t="n">
+      <c r="E268" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="0" t="s">
+    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A269" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B267" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C267" s="0" t="n">
+      <c r="B269" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C269" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="D267" s="0" t="n">
+      <c r="D269" s="2" t="n">
         <v>0.39</v>
       </c>
-      <c r="E267" s="0" t="n">
+      <c r="E269" s="2" t="n">
         <v>26.714</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="0" t="s">
+    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A270" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B268" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C268" s="0" t="n">
+      <c r="B270" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C270" s="2" t="n">
         <v>3.32097367999354</v>
       </c>
-      <c r="D268" s="0" t="n">
+      <c r="D270" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E268" s="0" t="n">
+      <c r="E270" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="0" t="s">
+    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A271" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B269" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C269" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D269" s="0" t="n">
+      <c r="B271" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E269" s="0" t="n">
+      <c r="E271" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="0" t="s">
+    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A272" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B270" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C270" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D270" s="0" t="n">
+      <c r="B272" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E270" s="0" t="n">
+      <c r="E272" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="0" t="s">
+    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A273" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B271" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C271" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D271" s="0" t="n">
+      <c r="B273" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E271" s="0" t="n">
+      <c r="E273" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="0" t="s">
+    <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A274" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B272" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C272" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D272" s="0" t="n">
+      <c r="B274" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E272" s="0" t="n">
+      <c r="E274" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="0" t="s">
+    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A275" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B273" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C273" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D273" s="0" t="n">
+      <c r="B275" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E273" s="0" t="n">
+      <c r="E275" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="0" t="s">
+    <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A276" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B274" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C274" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D274" s="0" t="n">
+      <c r="B276" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E274" s="0" t="n">
+      <c r="E276" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="0" t="s">
+    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A277" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B275" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C275" s="0" t="n">
+      <c r="B277" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C277" s="2" t="n">
         <v>-15.902</v>
       </c>
-      <c r="D275" s="0" t="n">
+      <c r="D277" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E275" s="0" t="n">
+      <c r="E277" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="0" t="s">
+    <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A278" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B276" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C276" s="0" t="n">
+      <c r="B278" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C278" s="2" t="n">
         <v>-1.13999847799564</v>
       </c>
-      <c r="D276" s="0" t="n">
+      <c r="D278" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E276" s="0" t="n">
+      <c r="E278" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="0" t="s">
+    <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A279" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B277" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C277" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D277" s="0" t="n">
+      <c r="B279" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E277" s="0" t="n">
+      <c r="E279" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="0" t="s">
+    <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A280" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B278" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C278" s="0" t="n">
+      <c r="B280" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C280" s="2" t="n">
         <v>-5.59031902059655</v>
       </c>
-      <c r="D278" s="0" t="n">
+      <c r="D280" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E278" s="0" t="n">
+      <c r="E280" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="0" t="s">
+    <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A281" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B279" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C279" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D279" s="0" t="n">
+      <c r="B281" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E279" s="0" t="n">
+      <c r="E281" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="0" t="s">
+    <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A282" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B280" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C280" s="0" t="n">
+      <c r="B282" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C282" s="2" t="n">
         <v>2.69160499572573</v>
       </c>
-      <c r="D280" s="0" t="n">
+      <c r="D282" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E280" s="0" t="n">
+      <c r="E282" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="0" t="s">
+    <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A283" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B281" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C281" s="0" t="n">
+      <c r="B283" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C283" s="2" t="n">
         <v>-2.69160499572692</v>
       </c>
-      <c r="D281" s="0" t="n">
+      <c r="D283" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E281" s="0" t="n">
+      <c r="E283" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="0" t="s">
+    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A284" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B282" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C282" s="0" t="n">
+      <c r="B284" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C284" s="2" t="n">
         <v>-2.69160499574415</v>
       </c>
-      <c r="D282" s="0" t="n">
+      <c r="D284" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E282" s="0" t="n">
+      <c r="E284" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="0" t="s">
+    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A285" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B283" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C283" s="0" t="n">
+      <c r="B285" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C285" s="2" t="n">
         <v>-3.41514599576398</v>
       </c>
-      <c r="D283" s="0" t="n">
+      <c r="D285" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E283" s="0" t="n">
+      <c r="E285" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="0" t="s">
+    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A286" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B284" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C284" s="0" t="n">
+      <c r="B286" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C286" s="2" t="n">
         <v>-4.2738539957672</v>
       </c>
-      <c r="D284" s="0" t="n">
+      <c r="D286" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E284" s="0" t="n">
+      <c r="E286" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="0" t="s">
+    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A287" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B285" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C285" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D285" s="0" t="n">
+      <c r="B287" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E285" s="0" t="n">
+      <c r="E287" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="0" t="s">
+    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B286" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C286" s="0" t="n">
+      <c r="B288" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C288" s="2" t="n">
         <v>3.73003729455362</v>
       </c>
-      <c r="D286" s="0" t="n">
+      <c r="D288" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E286" s="0" t="n">
+      <c r="E288" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A287" s="0" t="s">
+    <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A289" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B287" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C287" s="0" t="n">
+      <c r="B289" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C289" s="2" t="n">
         <v>7.75208185831655</v>
       </c>
-      <c r="D287" s="0" t="n">
+      <c r="D289" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E287" s="0" t="n">
+      <c r="E289" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A288" s="0" t="s">
+    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A290" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B288" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C288" s="0" t="n">
+      <c r="B290" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C290" s="2" t="n">
         <v>0.655464183289113</v>
       </c>
-      <c r="D288" s="0" t="n">
+      <c r="D290" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E288" s="0" t="n">
+      <c r="E290" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A289" s="0" t="s">
+    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A291" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B289" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C289" s="0" t="n">
+      <c r="B291" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C291" s="2" t="n">
         <v>5.56328562058054</v>
       </c>
-      <c r="D289" s="0" t="n">
+      <c r="D291" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E289" s="0" t="n">
+      <c r="E291" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="0" t="s">
+    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A292" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B290" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C290" s="0" t="n">
+      <c r="B292" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C292" s="2" t="n">
         <v>4.90782143729143</v>
       </c>
-      <c r="D290" s="0" t="n">
+      <c r="D292" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E290" s="0" t="n">
+      <c r="E292" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="0" t="s">
+    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A293" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B291" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C291" s="0" t="n">
+      <c r="B293" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C293" s="2" t="n">
         <v>1.97412301242644</v>
       </c>
-      <c r="D291" s="0" t="n">
+      <c r="D293" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E291" s="0" t="n">
+      <c r="E293" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="0" t="s">
+    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A294" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B292" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C292" s="0" t="n">
+      <c r="B294" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C294" s="2" t="n">
         <v>2.93369842486498</v>
       </c>
-      <c r="D292" s="0" t="n">
+      <c r="D294" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E292" s="0" t="n">
+      <c r="E294" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="0" t="s">
+    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A295" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B293" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C293" s="0" t="n">
+      <c r="B295" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C295" s="2" t="n">
         <v>1.56385141243138</v>
       </c>
-      <c r="D293" s="0" t="n">
+      <c r="D295" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E293" s="0" t="n">
+      <c r="E295" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A294" s="0" t="s">
+    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A296" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B294" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C294" s="0" t="n">
+      <c r="B296" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C296" s="2" t="n">
         <v>1.36984701243361</v>
       </c>
-      <c r="D294" s="0" t="n">
+      <c r="D296" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E294" s="0" t="n">
+      <c r="E296" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A295" s="0" t="s">
+    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A297" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B295" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C295" s="0" t="n">
+      <c r="B297" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C297" s="2" t="n">
         <v>2.01611019852015</v>
       </c>
-      <c r="D295" s="0" t="n">
+      <c r="D297" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E295" s="0" t="n">
+      <c r="E297" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="0" t="s">
+    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B296" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C296" s="0" t="n">
+      <c r="B298" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C298" s="2" t="n">
         <v>2.9717886997229</v>
       </c>
-      <c r="D296" s="0" t="n">
+      <c r="D298" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E296" s="0" t="n">
+      <c r="E298" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A297" s="0" t="s">
+    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A299" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B297" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C297" s="0" t="n">
+      <c r="B299" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C299" s="2" t="n">
         <v>3.1554008705399</v>
       </c>
-      <c r="D297" s="0" t="n">
+      <c r="D299" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E297" s="0" t="n">
+      <c r="E299" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="0" t="s">
+    <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A300" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B298" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C298" s="0" t="n">
+      <c r="B300" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C300" s="2" t="n">
         <v>3.0389493627578</v>
       </c>
-      <c r="D298" s="0" t="n">
+      <c r="D300" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E298" s="0" t="n">
+      <c r="E300" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A299" s="0" t="s">
+    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A301" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B299" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C299" s="0" t="n">
+      <c r="B301" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C301" s="2" t="n">
         <v>2.35198296275279</v>
       </c>
-      <c r="D299" s="0" t="n">
+      <c r="D301" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E299" s="0" t="n">
+      <c r="E301" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A300" s="0" t="s">
+    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A302" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B300" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C300" s="0" t="n">
+      <c r="B302" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C302" s="2" t="n">
         <v>18.3704344705194</v>
       </c>
-      <c r="D300" s="0" t="n">
+      <c r="D302" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E300" s="0" t="n">
+      <c r="E302" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A301" s="0" t="s">
+    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A303" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B301" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C301" s="0" t="n">
+      <c r="B303" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C303" s="2" t="n">
         <v>17.2304359925238</v>
       </c>
-      <c r="D301" s="0" t="n">
+      <c r="D303" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E301" s="0" t="n">
+      <c r="E303" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A302" s="0" t="s">
+    <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A304" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B302" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C302" s="0" t="n">
+      <c r="B304" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C304" s="2" t="n">
         <v>4.95070497175081</v>
       </c>
-      <c r="D302" s="0" t="n">
+      <c r="D304" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E302" s="0" t="n">
+      <c r="E304" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A303" s="0" t="s">
+    <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A305" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B303" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C303" s="0" t="n">
+      <c r="B305" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C305" s="2" t="n">
         <v>12.396182528591</v>
       </c>
-      <c r="D303" s="0" t="n">
+      <c r="D305" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E303" s="0" t="n">
+      <c r="E305" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="0" t="s">
+    <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A306" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B304" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C304" s="0" t="n">
+      <c r="B306" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C306" s="2" t="n">
         <v>0.116451507786479</v>
       </c>
-      <c r="D304" s="0" t="n">
+      <c r="D306" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E304" s="0" t="n">
+      <c r="E306" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="0" t="s">
+    <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A307" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B305" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C305" s="0" t="n">
+      <c r="B307" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C307" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="D305" s="0" t="n">
+      <c r="D307" s="2" t="n">
         <v>0.51</v>
       </c>
-      <c r="E305" s="0" t="n">
+      <c r="E307" s="2" t="n">
         <v>15.902</v>
       </c>
     </row>
